--- a/docs/control-plane/04_DOMAIN_CLOUDFLARE_REGISTRY.xlsx
+++ b/docs/control-plane/04_DOMAIN_CLOUDFLARE_REGISTRY.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="173">
   <si>
     <t>04_DOMAIN_CLOUDFLARE_REGISTRY</t>
   </si>
@@ -47,6 +47,12 @@
     <t>CRITICAL: NEVER STORE PASSWORDS, API KEYS, SERVICE-ROLE KEYS, PRIVATE CERTIFICATES, SMTP PASSWORDS, OR R2 SECRETS IN THIS WORKBOOK. USE SECURE ENVIRONMENT REFERENCES ONLY.</t>
   </si>
   <si>
+    <t>Canonical Production Subdomain</t>
+  </si>
+  <si>
+    <t>https://erp.arivahly.in (Parent domain: arivahly.in)</t>
+  </si>
+  <si>
     <t>AI Operating Constraint 1</t>
   </si>
   <si>
@@ -71,10 +77,16 @@
     <t>UNKNOWN means unknown. Do not guess. If a field is uncertain, record NEEDS_VERIFICATION.</t>
   </si>
   <si>
+    <t>MCP Security Boundary</t>
+  </si>
+  <si>
+    <t>MCP is DISABLED and BLOCKED from public routing. MCP tools must remain internal/local only.</t>
+  </si>
+  <si>
     <t>Last Audit Date</t>
   </si>
   <si>
-    <t>2026-09-05T13:10:00+05:30 (Release v1.1.2-online-production-hardened)</t>
+    <t>2026-09-05T13:20:00+05:30 (Release v1.1.2-online-production-hardened)</t>
   </si>
   <si>
     <t>Domain_ID</t>
@@ -113,13 +125,13 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>DOM-MAATARA-PROD</t>
-  </si>
-  <si>
-    <t>maatarajewellers.shop</t>
-  </si>
-  <si>
-    <t>Primary Production SaaS Domain</t>
+    <t>DOM-ARIVAHLY-ERP</t>
+  </si>
+  <si>
+    <t>erp.arivahly.in</t>
+  </si>
+  <si>
+    <t>Official Production Online Managed ERP Subdomain</t>
   </si>
   <si>
     <t>ENV-ONLINE-PROD</t>
@@ -146,19 +158,19 @@
     <t>2026-09-05</t>
   </si>
   <si>
-    <t>Full TLS 1.3 encryption with HTTP/2 and 0-RTT</t>
-  </si>
-  <si>
-    <t>DOM-MAATARA-WWW</t>
-  </si>
-  <si>
-    <t>www.maatarajewellers.shop</t>
-  </si>
-  <si>
-    <t>Production CNAME Alias</t>
-  </si>
-  <si>
-    <t>Auto-redirects to apex domain</t>
+    <t>Canonical human-facing production URL with TLS 1.3, HTTP/2, 0-RTT</t>
+  </si>
+  <si>
+    <t>DOM-ARIVAHLY-ROOT</t>
+  </si>
+  <si>
+    <t>arivahly.in</t>
+  </si>
+  <si>
+    <t>Parent Apex Domain</t>
+  </si>
+  <si>
+    <t>Parent zone in Cloudflare; ERP hosted on erp.arivahly.in subdomain</t>
   </si>
   <si>
     <t>Record_Type</t>
@@ -182,69 +194,63 @@
     <t>CNAME / A</t>
   </si>
   <si>
+    <t>erp</t>
+  </si>
+  <si>
+    <t>Hostinger Web Origin IP</t>
+  </si>
+  <si>
+    <t>YES (Orange Cloud)</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>Production Online ERP frontend &amp; API routing</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Proxied through Cloudflare edge to Hostinger document root</t>
+  </si>
+  <si>
+    <t>TXT</t>
+  </si>
+  <si>
+    <t>_dmarc</t>
+  </si>
+  <si>
+    <t>v=DMARC1; p=reject; rua=mailto:admin@arivahly.in</t>
+  </si>
+  <si>
+    <t>NO (DNS Only)</t>
+  </si>
+  <si>
+    <t>DMARC email security policy</t>
+  </si>
+  <si>
+    <t>Enforces strict rejection of spoofed emails</t>
+  </si>
+  <si>
+    <t>hostingermail._domainkey</t>
+  </si>
+  <si>
+    <t>Hostinger DKIM Public Key</t>
+  </si>
+  <si>
+    <t>DKIM cryptographic email signature</t>
+  </si>
+  <si>
+    <t>Validates transactional email authenticity</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
     <t>@</t>
   </si>
   <si>
-    <t>Hostinger Web Origin IP</t>
-  </si>
-  <si>
-    <t>YES (Orange Cloud)</t>
-  </si>
-  <si>
-    <t>Auto</t>
-  </si>
-  <si>
-    <t>Main web frontend and API routing</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>Proxied through Cloudflare edge</t>
-  </si>
-  <si>
-    <t>CNAME</t>
-  </si>
-  <si>
-    <t>www</t>
-  </si>
-  <si>
-    <t>WWW redirect alias</t>
-  </si>
-  <si>
-    <t>TXT</t>
-  </si>
-  <si>
-    <t>_dmarc</t>
-  </si>
-  <si>
-    <t>v=DMARC1; p=reject; rua=mailto:admin@maatarajewellers.shop</t>
-  </si>
-  <si>
-    <t>NO (DNS Only)</t>
-  </si>
-  <si>
-    <t>DMARC email security policy</t>
-  </si>
-  <si>
-    <t>Enforces strict rejection of spoofed emails</t>
-  </si>
-  <si>
-    <t>hostingermail._domainkey</t>
-  </si>
-  <si>
-    <t>Hostinger DKIM Public Key</t>
-  </si>
-  <si>
-    <t>DKIM cryptographic email signature</t>
-  </si>
-  <si>
-    <t>Validates transactional email authenticity</t>
-  </si>
-  <si>
-    <t>MX</t>
-  </si>
-  <si>
     <t>mx1.hostinger.com</t>
   </si>
   <si>
@@ -296,19 +302,19 @@
     <t>Bot Fight Mode Active</t>
   </si>
   <si>
-    <t>BLOCKED (GPTBot, Claude, etc.)</t>
+    <t>BLOCKED (GPTBot, ClaudeBot, Bytespider, etc.)</t>
   </si>
   <si>
     <t>120 req/min API, 10 req/min Auth</t>
   </si>
   <si>
-    <t>HSTS, X-Frame, Nosniff, CSP</t>
-  </si>
-  <si>
-    <t>no-store on /api/*, cache on static</t>
-  </si>
-  <si>
-    <t>Restricted to Production Origins</t>
+    <t>HSTS, X-Frame-Options: SAMEORIGIN, X-Content-Type-Options: nosniff, CSP</t>
+  </si>
+  <si>
+    <t>no-store on /api/*, cache on static assets</t>
+  </si>
+  <si>
+    <t>Restricted to https://erp.arivahly.in</t>
   </si>
   <si>
     <t>Challenge on Suspicious IPs</t>
@@ -323,7 +329,7 @@
     <t>HARDENED</t>
   </si>
   <si>
-    <t>Complies with CLOUDFLARE_SECURITY_CONFIGURATION.md</t>
+    <t>Complies with CLOUDFLARE_SECURITY_CONFIGURATION.md; MCP is DISABLED</t>
   </si>
   <si>
     <t>URL_ID</t>
@@ -353,7 +359,7 @@
     <t>URL-001</t>
   </si>
   <si>
-    <t>https://maatarajewellers.shop</t>
+    <t>https://erp.arivahly.in</t>
   </si>
   <si>
     <t>Main ERP Landing / Application</t>
@@ -371,13 +377,13 @@
     <t>Loads SPA bundle with AuthGate</t>
   </si>
   <si>
-    <t>Root frontend entry</t>
+    <t>Root frontend entry for Online ERP</t>
   </si>
   <si>
     <t>URL-002</t>
   </si>
   <si>
-    <t>https://maatarajewellers.shop/login</t>
+    <t>https://erp.arivahly.in/login</t>
   </si>
   <si>
     <t>Universal Application Login</t>
@@ -395,7 +401,7 @@
     <t>URL-003</t>
   </si>
   <si>
-    <t>https://maatarajewellers.shop/accept-invitation</t>
+    <t>https://erp.arivahly.in/accept-invitation</t>
   </si>
   <si>
     <t>Universal Invitation Acceptance Entry</t>
@@ -413,7 +419,7 @@
     <t>URL-004</t>
   </si>
   <si>
-    <t>https://maatarajewellers.shop/customer-portal</t>
+    <t>https://erp.arivahly.in/customer-portal</t>
   </si>
   <si>
     <t>Customer Ledger &amp; Order Portal</t>
@@ -434,7 +440,7 @@
     <t>URL-005</t>
   </si>
   <si>
-    <t>https://maatarajewellers.shop/karigar-portal</t>
+    <t>https://erp.arivahly.in/karigar-portal</t>
   </si>
   <si>
     <t>Karigar Gold &amp; Job Card Portal</t>
@@ -452,7 +458,7 @@
     <t>URL-006</t>
   </si>
   <si>
-    <t>https://maatarajewellers.shop/company-admin</t>
+    <t>https://erp.arivahly.in/company-admin</t>
   </si>
   <si>
     <t>Authoritative SaaS Admin Control Center</t>
@@ -473,7 +479,7 @@
     <t>URL-007</t>
   </si>
   <si>
-    <t>https://maatarajewellers.shop/verify/invoice/:token</t>
+    <t>https://erp.arivahly.in/verify/invoice/:token</t>
   </si>
   <si>
     <t>Public Invoice QR Verification Endpoint</t>
@@ -494,7 +500,7 @@
     <t>URL-008</t>
   </si>
   <si>
-    <t>https://maatarajewellers.shop/api/health.php</t>
+    <t>https://erp.arivahly.in/api/health.php</t>
   </si>
   <si>
     <t>System &amp; Diagnostic Health Probe</t>
@@ -512,7 +518,7 @@
     <t>URL-009</t>
   </si>
   <si>
-    <t>https://maatarajewellers.shop/api/webhooks/dispatcher.php</t>
+    <t>https://erp.arivahly.in/api/webhooks/dispatcher.php</t>
   </si>
   <si>
     <t>Central Webhook Broker</t>
@@ -975,7 +981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1060,6 +1066,22 @@
       </c>
       <c r="B11" s="4" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1073,142 +1095,142 @@
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="25" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="49" customWidth="1"/>
+    <col min="13" max="13" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="K3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="M3" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1219,230 +1241,195 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="54" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="38" customWidth="1"/>
+    <col min="8" max="8" width="48" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="47" customWidth="1"/>
+    <col min="11" max="11" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="G3" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1459,12 +1446,12 @@
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="4" max="4" width="49" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="31" customWidth="1"/>
-    <col min="8" max="8" width="39" customWidth="1"/>
-    <col min="9" max="9" width="36" customWidth="1"/>
+    <col min="7" max="7" width="54" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
+    <col min="9" max="9" width="41" customWidth="1"/>
     <col min="10" max="10" width="31" customWidth="1"/>
     <col min="11" max="11" width="25" customWidth="1"/>
     <col min="12" max="12" width="28" customWidth="1"/>
@@ -1475,96 +1462,96 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1594,382 +1581,382 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
